--- a/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{672DDAAA-6E3D-4418-B51C-CD07F8B16C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{92BCC415-AF48-4F2E-ABD9-AD62020EF5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1563,10 +1563,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>SaD,FaD,WaD,RaD,RaP,FaP,SaP,WaP</t>
+    <t>WaD,RaD,WaP,FaD,SaD,FaP,SaP,RaP</t>
   </si>
   <si>
-    <t>FaP,SaP,SaN,WaN,RaP,RaN,FaN,WaP</t>
+    <t>FaN,RaN,RaP,FaP,SaP,WaP,SaN,WaN</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaP,SaP,SaN,WaN,RaP,RaN,FaN,WaP</v>
+        <v>FaN,RaN,RaP,FaP,SaP,WaP,SaN,WaN</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>SaD,FaD,WaD,RaD,RaP,FaP,SaP,WaP</v>
+        <v>WaD,RaD,WaP,FaD,SaD,FaP,SaP,RaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2289,7 +2289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8C0269F-F60D-4030-B798-0F7D7BF41BCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5849E8F-91A1-48E2-8D00-BEB1D1457D8C}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2373,7 +2373,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D065A35-03EC-4144-9B34-F47BE7535ED4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9983786-977C-4005-B0FE-A12DA11D5093}">
   <dimension ref="B9:O1390"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36155,7 +36155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C900F0-F29F-4B84-87EE-EC0093B5CDAD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE5B3E1-C06C-420D-8C68-A216D5E8F78A}">
   <dimension ref="B9:BL225"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57043,7 +57043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{437D1FB8-F4CB-4D68-B9CB-83E5D611B322}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3264219F-15C1-4997-995D-EF781062B952}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57241,7 +57241,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8BBBF5A-E6C8-43C3-A88F-3131F2DF1BF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D996FB-AF39-4415-9530-BDE461EF7249}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57532,7 +57532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDFC00B-B550-4890-9EF9-33BFB4BF923C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11AA3ED-5A28-4CC5-863B-098BFBC25FAF}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57691,7 +57691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCCE5694-65F8-4BC0-A09A-1024C52CC551}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98899F19-8ACA-49AD-BC77-1F099C6CC74A}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57723,7 +57723,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.40429999999999994</v>
+        <v>0.40430000000000005</v>
       </c>
       <c r="E11" t="s">
         <v>514</v>
@@ -57765,7 +57765,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.45619999999999994</v>
+        <v>0.45619999999999999</v>
       </c>
       <c r="E14" t="s">
         <v>514</v>
@@ -57821,7 +57821,7 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>0.44070000000000004</v>
+        <v>0.44069999999999993</v>
       </c>
       <c r="E18" t="s">
         <v>514</v>
@@ -57849,7 +57849,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.49373333333333336</v>
+        <v>0.4937333333333333</v>
       </c>
       <c r="E20" t="s">
         <v>514</v>
@@ -57891,7 +57891,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.47613333333333335</v>
+        <v>0.4761333333333333</v>
       </c>
       <c r="E23" t="s">
         <v>514</v>
@@ -57919,7 +57919,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.44693333333333335</v>
+        <v>0.44693333333333324</v>
       </c>
       <c r="E25" t="s">
         <v>514</v>
@@ -57933,7 +57933,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.57236666666666669</v>
+        <v>0.5723666666666668</v>
       </c>
       <c r="E26" t="s">
         <v>514</v>
@@ -58003,7 +58003,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.53999999999999992</v>
+        <v>0.54</v>
       </c>
       <c r="E31" t="s">
         <v>514</v>
@@ -58031,7 +58031,7 @@
         <v>43</v>
       </c>
       <c r="D33">
-        <v>0.45806666666666662</v>
+        <v>0.45806666666666668</v>
       </c>
       <c r="E33" t="s">
         <v>514</v>
@@ -58059,7 +58059,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.4864</v>
+        <v>0.48639999999999994</v>
       </c>
       <c r="E35" t="s">
         <v>514</v>
@@ -58185,7 +58185,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.54423333333333335</v>
+        <v>0.54423333333333324</v>
       </c>
       <c r="E44" t="s">
         <v>514</v>
@@ -58199,7 +58199,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.55666666666666664</v>
+        <v>0.55666666666666675</v>
       </c>
       <c r="E45" t="s">
         <v>514</v>
@@ -58213,7 +58213,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.62726666666666664</v>
+        <v>0.62726666666666675</v>
       </c>
       <c r="E46" t="s">
         <v>514</v>
@@ -58227,7 +58227,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.49716666666666676</v>
+        <v>0.4971666666666667</v>
       </c>
       <c r="E47" t="s">
         <v>514</v>
@@ -58269,7 +58269,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.60400000000000009</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="E50" t="s">
         <v>514</v>
@@ -58339,7 +58339,7 @@
         <v>37</v>
       </c>
       <c r="D55">
-        <v>0.57473333333333343</v>
+        <v>0.57473333333333321</v>
       </c>
       <c r="E55" t="s">
         <v>514</v>
@@ -58367,7 +58367,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.55299999999999994</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="E57" t="s">
         <v>514</v>
@@ -58381,7 +58381,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.66103333333333347</v>
+        <v>0.66103333333333336</v>
       </c>
       <c r="E58" t="s">
         <v>514</v>
@@ -58395,7 +58395,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.57526666666666659</v>
+        <v>0.5752666666666667</v>
       </c>
       <c r="E59" t="s">
         <v>514</v>
@@ -58437,7 +58437,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.61239999999999994</v>
+        <v>0.61240000000000006</v>
       </c>
       <c r="E62" t="s">
         <v>514</v>
@@ -58465,7 +58465,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.61703333333333332</v>
+        <v>0.61703333333333321</v>
       </c>
       <c r="E64" t="s">
         <v>514</v>
@@ -58493,7 +58493,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.68866666666666665</v>
+        <v>0.68866666666666676</v>
       </c>
       <c r="E66" t="s">
         <v>514</v>
@@ -58563,7 +58563,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.56470000000000009</v>
+        <v>0.56469999999999998</v>
       </c>
       <c r="E71" t="s">
         <v>514</v>
@@ -58703,7 +58703,7 @@
         <v>43</v>
       </c>
       <c r="D81">
-        <v>0.3370333333333333</v>
+        <v>0.33703333333333335</v>
       </c>
       <c r="E81" t="s">
         <v>514</v>
@@ -58801,7 +58801,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.48299999999999993</v>
+        <v>0.48300000000000004</v>
       </c>
       <c r="E88" t="s">
         <v>514</v>
@@ -58871,7 +58871,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.39333333333333331</v>
+        <v>0.39333333333333337</v>
       </c>
       <c r="E93" t="s">
         <v>514</v>
@@ -58955,7 +58955,7 @@
         <v>37</v>
       </c>
       <c r="D99">
-        <v>0.44413333333333327</v>
+        <v>0.44413333333333332</v>
       </c>
       <c r="E99" t="s">
         <v>514</v>
@@ -58969,7 +58969,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.51993333333333336</v>
+        <v>0.51993333333333325</v>
       </c>
       <c r="E100" t="s">
         <v>514</v>
@@ -59081,7 +59081,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.63253333333333328</v>
+        <v>0.63253333333333339</v>
       </c>
       <c r="E108" t="s">
         <v>514</v>
@@ -59235,7 +59235,7 @@
         <v>37</v>
       </c>
       <c r="D119">
-        <v>0.5024333333333334</v>
+        <v>0.50243333333333329</v>
       </c>
       <c r="E119" t="s">
         <v>514</v>

--- a/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_BRA_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{92BCC415-AF48-4F2E-ABD9-AD62020EF5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF9677E8-39FA-408C-9644-33C629ADB862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1563,10 +1563,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>WaD,RaD,WaP,FaD,SaD,FaP,SaP,RaP</t>
+    <t>FaD,SaD,WaD,WaP,RaD,FaP,SaP,RaP</t>
   </si>
   <si>
-    <t>FaN,RaN,RaP,FaP,SaP,WaP,SaN,WaN</t>
+    <t>RaP,FaN,FaP,SaP,RaN,SaN,WaN,WaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaN,RaN,RaP,FaP,SaP,WaP,SaN,WaN</v>
+        <v>RaP,FaN,FaP,SaP,RaN,SaN,WaN,WaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>WaD,RaD,WaP,FaD,SaD,FaP,SaP,RaP</v>
+        <v>FaD,SaD,WaD,WaP,RaD,FaP,SaP,RaP</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -2289,7 +2289,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5849E8F-91A1-48E2-8D00-BEB1D1457D8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E9D7DF5-6E1C-420F-BAC4-541C287100B2}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2373,7 +2373,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9983786-977C-4005-B0FE-A12DA11D5093}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{249D7472-F2FC-44C1-A212-7E920F0587DB}">
   <dimension ref="B9:O1390"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -36155,7 +36155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE5B3E1-C06C-420D-8C68-A216D5E8F78A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CFB6C7B-7281-499A-9805-91EABAA32C74}">
   <dimension ref="B9:BL225"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57043,7 +57043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3264219F-15C1-4997-995D-EF781062B952}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC16894-D679-450F-87E4-46CC2473860D}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57241,7 +57241,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83D996FB-AF39-4415-9530-BDE461EF7249}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22ED7EC-F98A-4C6A-B0B6-344F4A01743B}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57532,7 +57532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11AA3ED-5A28-4CC5-863B-098BFBC25FAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C9CA96-642A-4440-9C3E-BACF292511A1}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57691,7 +57691,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98899F19-8ACA-49AD-BC77-1F099C6CC74A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAD73D62-638F-4BBD-8E91-59E17D498448}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -57723,7 +57723,7 @@
         <v>37</v>
       </c>
       <c r="D11">
-        <v>0.40430000000000005</v>
+        <v>0.40429999999999994</v>
       </c>
       <c r="E11" t="s">
         <v>514</v>
@@ -57765,7 +57765,7 @@
         <v>45</v>
       </c>
       <c r="D14">
-        <v>0.45619999999999999</v>
+        <v>0.45619999999999994</v>
       </c>
       <c r="E14" t="s">
         <v>514</v>
@@ -57821,7 +57821,7 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>0.44069999999999993</v>
+        <v>0.44070000000000004</v>
       </c>
       <c r="E18" t="s">
         <v>514</v>
@@ -57835,7 +57835,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.42230000000000006</v>
+        <v>0.42229999999999995</v>
       </c>
       <c r="E19" t="s">
         <v>514</v>
@@ -57849,7 +57849,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.4937333333333333</v>
+        <v>0.49373333333333336</v>
       </c>
       <c r="E20" t="s">
         <v>514</v>
@@ -57933,7 +57933,7 @@
         <v>45</v>
       </c>
       <c r="D26">
-        <v>0.5723666666666668</v>
+        <v>0.57236666666666669</v>
       </c>
       <c r="E26" t="s">
         <v>514</v>
@@ -58059,7 +58059,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>0.48639999999999994</v>
+        <v>0.4864</v>
       </c>
       <c r="E35" t="s">
         <v>514</v>
@@ -58087,7 +58087,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.50753333333333328</v>
+        <v>0.50753333333333339</v>
       </c>
       <c r="E37" t="s">
         <v>514</v>
@@ -58185,7 +58185,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.54423333333333324</v>
+        <v>0.54423333333333335</v>
       </c>
       <c r="E44" t="s">
         <v>514</v>
@@ -58199,7 +58199,7 @@
         <v>43</v>
       </c>
       <c r="D45">
-        <v>0.55666666666666675</v>
+        <v>0.55666666666666664</v>
       </c>
       <c r="E45" t="s">
         <v>514</v>
@@ -58213,7 +58213,7 @@
         <v>45</v>
       </c>
       <c r="D46">
-        <v>0.62726666666666675</v>
+        <v>0.62726666666666664</v>
       </c>
       <c r="E46" t="s">
         <v>514</v>
@@ -58227,7 +58227,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.4971666666666667</v>
+        <v>0.49716666666666659</v>
       </c>
       <c r="E47" t="s">
         <v>514</v>
@@ -58269,7 +58269,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.60399999999999998</v>
+        <v>0.60400000000000009</v>
       </c>
       <c r="E50" t="s">
         <v>514</v>
@@ -58339,7 +58339,7 @@
         <v>37</v>
       </c>
       <c r="D55">
-        <v>0.57473333333333321</v>
+        <v>0.57473333333333332</v>
       </c>
       <c r="E55" t="s">
         <v>514</v>
@@ -58367,7 +58367,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.55300000000000005</v>
+        <v>0.55299999999999994</v>
       </c>
       <c r="E57" t="s">
         <v>514</v>
@@ -58381,7 +58381,7 @@
         <v>45</v>
       </c>
       <c r="D58">
-        <v>0.66103333333333336</v>
+        <v>0.66103333333333347</v>
       </c>
       <c r="E58" t="s">
         <v>514</v>
@@ -58395,7 +58395,7 @@
         <v>37</v>
       </c>
       <c r="D59">
-        <v>0.5752666666666667</v>
+        <v>0.57526666666666659</v>
       </c>
       <c r="E59" t="s">
         <v>514</v>
@@ -58437,7 +58437,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.61240000000000006</v>
+        <v>0.61239999999999994</v>
       </c>
       <c r="E62" t="s">
         <v>514</v>
@@ -58465,7 +58465,7 @@
         <v>41</v>
       </c>
       <c r="D64">
-        <v>0.61703333333333321</v>
+        <v>0.61703333333333332</v>
       </c>
       <c r="E64" t="s">
         <v>514</v>
@@ -58493,7 +58493,7 @@
         <v>45</v>
       </c>
       <c r="D66">
-        <v>0.68866666666666676</v>
+        <v>0.68866666666666665</v>
       </c>
       <c r="E66" t="s">
         <v>514</v>
@@ -58563,7 +58563,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.56469999999999998</v>
+        <v>0.56470000000000009</v>
       </c>
       <c r="E71" t="s">
         <v>514</v>
@@ -58703,7 +58703,7 @@
         <v>43</v>
       </c>
       <c r="D81">
-        <v>0.33703333333333335</v>
+        <v>0.3370333333333333</v>
       </c>
       <c r="E81" t="s">
         <v>514</v>
@@ -58801,7 +58801,7 @@
         <v>41</v>
       </c>
       <c r="D88">
-        <v>0.48300000000000004</v>
+        <v>0.48299999999999993</v>
       </c>
       <c r="E88" t="s">
         <v>514</v>
@@ -58969,7 +58969,7 @@
         <v>41</v>
       </c>
       <c r="D100">
-        <v>0.51993333333333325</v>
+        <v>0.51993333333333336</v>
       </c>
       <c r="E100" t="s">
         <v>514</v>
@@ -59039,7 +59039,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.50813333333333333</v>
+        <v>0.50813333333333344</v>
       </c>
       <c r="E105" t="s">
         <v>514</v>
@@ -59081,7 +59081,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.63253333333333339</v>
+        <v>0.63253333333333328</v>
       </c>
       <c r="E108" t="s">
         <v>514</v>
@@ -59179,7 +59179,7 @@
         <v>37</v>
       </c>
       <c r="D115">
-        <v>0.4995</v>
+        <v>0.49950000000000006</v>
       </c>
       <c r="E115" t="s">
         <v>514</v>
@@ -59263,7 +59263,7 @@
         <v>43</v>
       </c>
       <c r="D121">
-        <v>0.54100000000000004</v>
+        <v>0.54099999999999993</v>
       </c>
       <c r="E121" t="s">
         <v>514</v>
@@ -59291,7 +59291,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.53180000000000005</v>
+        <v>0.53179999999999994</v>
       </c>
       <c r="E123" t="s">
         <v>514</v>
